--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484172_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484172_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3985</v>
+        <v>6.0629</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3121</v>
+        <v>3.8643</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0864</v>
+        <v>2.1986</v>
       </c>
       <c r="G2" t="n">
         <v>3.232</v>
@@ -610,13 +610,13 @@
         <v>3.5709</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1462</v>
+        <v>0.8106</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2358</v>
+        <v>0.788</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0897</v>
+        <v>0.0226</v>
       </c>
       <c r="V2" t="n">
         <v>0.4332</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6376</v>
+        <v>2.6791</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1709</v>
+        <v>1.2979</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8085</v>
+        <v>1.3811</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5782</v>
+        <v>0.3118</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2649</v>
+        <v>-0.6908</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6867</v>
+        <v>1.0026</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5338000000000001</v>
+        <v>1.7481</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0912</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.6568</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0444</v>
+        <v>-1.4362</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7311</v>
+        <v>-0.782</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6867</v>
+        <v>-0.6542</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9919</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.6009</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3548</v>
+        <v>-0.1019</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4682</v>
+        <v>0.7027</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3373</v>
+        <v>3.3534</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.6194</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0455</v>
+        <v>1.3001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1132</v>
+        <v>0.2737</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9323</v>
+        <v>1.0264</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3118</v>
+        <v>-0.7991</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6908</v>
+        <v>-0.3483</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0026</v>
+        <v>-0.4508</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7481</v>
+        <v>-0.1563</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0912</v>
+        <v>0.4436</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6568</v>
+        <v>-0.5999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4362</v>
+        <v>-0.6428</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.782</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6542</v>
+        <v>0.149</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9677</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0327</v>
+        <v>0.4081</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2865</v>
+        <v>0.2155</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2539</v>
+        <v>0.1926</v>
       </c>
       <c r="V4" t="n">
-        <v>3.3534</v>
+        <v>0.6992</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6194</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-0.5073</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.392</v>
+        <v>1.1478</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.486</v>
+        <v>-0.8851</v>
       </c>
       <c r="F5" t="n">
-        <v>1.878</v>
+        <v>2.0329</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4826</v>
+        <v>-0.5782</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6354</v>
+        <v>-1.2649</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.118</v>
+        <v>0.6867</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6257</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2256</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1083</v>
+        <v>-0.0444</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.7311</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5182</v>
+        <v>0.6867</v>
       </c>
       <c r="P5" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.3968</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.9838</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.3806</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.4778</v>
-      </c>
       <c r="T5" t="n">
-        <v>-0.0566</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5344</v>
+        <v>-0.2438</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0713</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.247</v>
+        <v>0.4824</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6672</v>
+        <v>-1.4236</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9142</v>
+        <v>1.906</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7991</v>
+        <v>-0.4826</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3483</v>
+        <v>0.6354</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4508</v>
+        <v>-1.118</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1563</v>
+        <v>0.6257</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4436</v>
+        <v>1.2256</v>
       </c>
       <c r="L6" t="n">
         <v>-0.5999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6428</v>
+        <v>-1.1083</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.149</v>
+        <v>-0.5182</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.645</v>
+        <v>0.5682</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7254</v>
+        <v>0.0057</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0804</v>
+        <v>0.5625</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6992</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5073</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4503</v>
+        <v>0.0014</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1469</v>
+        <v>-0.9953</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3034</v>
+        <v>0.9967</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4877</v>
+        <v>0.8275</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2623</v>
+        <v>0.4686</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2254</v>
+        <v>0.3589</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0402</v>
+        <v>2.0768</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.7916</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>1.2852</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5279</v>
+        <v>-1.2493</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2623</v>
+        <v>-0.323</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2656</v>
+        <v>-0.9263</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5577</v>
+        <v>0.1658</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.187</v>
+        <v>-0.0963</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3707</v>
+        <v>0.2621</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8531</v>
+        <v>-0.2922</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7095</v>
+        <v>-0.0448</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.2473</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8275</v>
+        <v>-0.4877</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4686</v>
+        <v>-0.2623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3589</v>
+        <v>-0.2254</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0768</v>
+        <v>0.0402</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7916</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2852</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2493</v>
+        <v>-0.5279</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.323</v>
+        <v>-0.2623</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9263</v>
+        <v>-0.2656</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6887</v>
+        <v>-0.3996</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8105</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1218</v>
+        <v>-0.3146</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4548</v>
+        <v>-2.2636</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3642</v>
+        <v>-3.4435</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9093</v>
+        <v>1.1799</v>
       </c>
       <c r="G9" t="n">
         <v>-5.1163</v>
@@ -1156,13 +1156,13 @@
         <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3477</v>
+        <v>1.5389</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4479</v>
+        <v>0.3685</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8998</v>
+        <v>1.1703</v>
       </c>
       <c r="V9" t="n">
         <v>0.1234</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5219</v>
+        <v>-3.114</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6451</v>
+        <v>-4.9286</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1232</v>
+        <v>1.8146</v>
       </c>
       <c r="G10" t="n">
         <v>-5.3256</v>
@@ -1234,13 +1234,13 @@
         <v>3.1741</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5174</v>
+        <v>0.9253</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5047</v>
+        <v>0.2212</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0127</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0.096</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6684</v>
+        <v>-5.032</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2396</v>
+        <v>-4.6874</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4288</v>
+        <v>-0.3446</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3865</v>
@@ -1312,13 +1312,13 @@
         <v>2.3806</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0902</v>
+        <v>-0.2735</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6746</v>
+        <v>0.2268</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5844</v>
+        <v>-0.5003</v>
       </c>
       <c r="V11" t="n">
         <v>-1.785</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8731</v>
+        <v>-5.4496</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0501</v>
+        <v>-2.4582</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8231</v>
+        <v>-2.9914</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7019</v>
@@ -1390,13 +1390,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2845</v>
+        <v>-0.2919</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1814</v>
+        <v>-0.2267</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1031</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6542</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.101</v>
+        <v>-4.477699999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.0542</v>
+        <v>-13.4306</v>
       </c>
       <c r="F13" t="n">
-        <v>8.952999999999999</v>
+        <v>8.9529</v>
       </c>
       <c r="G13" t="n">
         <v>-12.5066</v>
@@ -1453,10 +1453,10 @@
         <v>-11.0671</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.2133</v>
+        <v>-7.213299999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.8538</v>
+        <v>-3.853800000000001</v>
       </c>
       <c r="P13" t="n">
         <v>2.9758</v>
@@ -1468,13 +1468,13 @@
         <v>23.8059</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8263</v>
+        <v>4.4496</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3332</v>
+        <v>1.9564</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4931</v>
+        <v>2.493</v>
       </c>
       <c r="V13" t="n">
         <v>0.6033000000000004</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2435</v>
+        <v>5.0081</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3987</v>
+        <v>2.0934</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8448</v>
+        <v>2.9147</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6369</v>
+        <v>5.2506</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9141</v>
+        <v>4.6211</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2772</v>
+        <v>0.6296</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1735</v>
+        <v>4.3379</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6127</v>
+        <v>3.8509</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4392</v>
+        <v>0.487</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4634</v>
+        <v>0.9127</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3014</v>
+        <v>0.7702</v>
       </c>
       <c r="O14" t="n">
-        <v>0.162</v>
+        <v>0.1425</v>
       </c>
       <c r="P14" t="n">
         <v>-0.1984</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9758</v>
+        <v>-2.1822</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7774</v>
+        <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5288</v>
+        <v>0.0765</v>
       </c>
       <c r="T14" t="n">
-        <v>0.669</v>
+        <v>-0.0623</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1402</v>
+        <v>0.1388</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7239</v>
+        <v>-0.1206</v>
       </c>
       <c r="W14" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2558</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2038</v>
+        <v>3.3448</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4812</v>
+        <v>1.4804</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7225</v>
+        <v>1.8644</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2506</v>
+        <v>4.6369</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6211</v>
+        <v>4.9141</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6296</v>
+        <v>-0.2772</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3379</v>
+        <v>4.1735</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8509</v>
+        <v>4.6127</v>
       </c>
       <c r="L15" t="n">
-        <v>0.487</v>
+        <v>-0.4392</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9127</v>
+        <v>0.4634</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7702</v>
+        <v>0.3014</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1425</v>
+        <v>0.162</v>
       </c>
       <c r="P15" t="n">
         <v>-0.1984</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9838</v>
+        <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7278</v>
+        <v>-0.3699</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6744</v>
+        <v>-0.2493</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0534</v>
+        <v>-0.1206</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1206</v>
+        <v>-0.7239</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1206</v>
+        <v>-1.2558</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9324</v>
+        <v>2.5331</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.142</v>
+        <v>0.2333</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0744</v>
+        <v>2.2998</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8591</v>
+        <v>0.8954</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2216</v>
+        <v>-1.0439</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6375</v>
+        <v>1.9394</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9398</v>
+        <v>0.6992</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0562</v>
+        <v>-1.0781</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8836000000000001</v>
+        <v>1.7773</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.1962</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1653</v>
+        <v>0.0342</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2461</v>
+        <v>0.162</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7935</v>
+        <v>2.1822</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9758</v>
+        <v>3.1741</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5181</v>
+        <v>-0.8106</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5667</v>
+        <v>-0.9465</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0486</v>
+        <v>0.1359</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6671</v>
+        <v>1.4724</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8692</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5366</v>
+        <v>2.1586</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3789</v>
+        <v>-0.244</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9155</v>
+        <v>2.4026</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8954</v>
+        <v>0.8591</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0439</v>
+        <v>0.2216</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9394</v>
+        <v>0.6375</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6992</v>
+        <v>0.9398</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0781</v>
+        <v>0.0562</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7773</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1962</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0342</v>
+        <v>0.1653</v>
       </c>
       <c r="O17" t="n">
-        <v>0.162</v>
+        <v>-0.2461</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1822</v>
+        <v>0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1741</v>
+        <v>2.9758</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.807</v>
+        <v>-0.2919</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5586</v>
+        <v>-0.6687</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2484</v>
+        <v>0.3768</v>
       </c>
       <c r="V17" t="n">
-        <v>0.266</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4724</v>
+        <v>1.6671</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2065</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4128</v>
+        <v>1.9851</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.211</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6099</v>
+        <v>0.774</v>
       </c>
       <c r="G18" t="n">
         <v>5.7902</v>
@@ -1858,13 +1858,13 @@
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5287</v>
+        <v>-0.9565</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1846</v>
+        <v>-0.7764</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3442</v>
+        <v>-0.1801</v>
       </c>
       <c r="V18" t="n">
         <v>-0.0713</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1848</v>
+        <v>0.8685</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2967</v>
+        <v>-1.5008</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4815</v>
+        <v>2.3693</v>
       </c>
       <c r="G19" t="n">
         <v>0.0806</v>
@@ -1936,13 +1936,13 @@
         <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1041</v>
+        <v>0.7879</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4932</v>
+        <v>0.2891</v>
       </c>
       <c r="U19" t="n">
-        <v>0.611</v>
+        <v>0.4988</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4623</v>
+        <v>-0.2939</v>
       </c>
       <c r="E20" t="n">
         <v>-1.7641</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3018</v>
+        <v>1.4701</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9486</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0125</v>
+        <v>0.1559</v>
       </c>
       <c r="T20" t="n">
         <v>0.3175</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3299</v>
+        <v>-0.1616</v>
       </c>
       <c r="V20" t="n">
         <v>2.2923</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>A. ELLENA VICENTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.921</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5383</v>
+        <v>0.1335</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6173</v>
+        <v>-1.0081</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.282</v>
+        <v>-0.5798</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.791</v>
+        <v>-0.5798</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.491</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7048</v>
+        <v>0.0202</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7449</v>
+        <v>0.0202</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5772</v>
+        <v>-0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.046</v>
+        <v>-0.6</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5312</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0832</v>
+        <v>-0.2947</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6859</v>
+        <v>0.1134</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3973</v>
+        <v>-0.4081</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.4085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ELLENA VICENTE</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9766</v>
+        <v>-1.5153</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0315</v>
+        <v>-3.0485</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0081</v>
+        <v>1.5331</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5798</v>
+        <v>-1.282</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5798</v>
+        <v>-0.791</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.491</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0202</v>
+        <v>-0.7048</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0202</v>
+        <v>-0.7449</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6</v>
+        <v>-0.5772</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6</v>
+        <v>-0.046</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.5312</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3968</v>
+        <v>0.4889</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0113</v>
+        <v>0.1758</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4081</v>
+        <v>0.3131</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7077</v>
+        <v>-1.5419</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3843</v>
+        <v>-1.0782</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3234</v>
+        <v>-0.4637</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6385</v>
@@ -2248,13 +2248,13 @@
         <v>0.3968</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1389</v>
+        <v>0.0269</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1247</v>
+        <v>0.1814</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0142</v>
+        <v>-0.1545</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3271</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7517</v>
+        <v>-1.9515</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0491</v>
+        <v>-2.6613</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2974</v>
+        <v>0.7098</v>
       </c>
       <c r="G24" t="n">
         <v>0.2718</v>
@@ -2326,13 +2326,13 @@
         <v>1.9838</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5016</v>
+        <v>-0.7015</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0001</v>
+        <v>-0.612</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5018</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5218</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5935</v>
+        <v>-3.2593</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1139</v>
+        <v>-3.8078</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5204</v>
+        <v>0.5485</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8295</v>
@@ -2404,13 +2404,13 @@
         <v>1.3887</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9109</v>
+        <v>-0.5767</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5611</v>
+        <v>-0.255</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3498</v>
+        <v>-0.3217</v>
       </c>
       <c r="V25" t="n">
         <v>-0.266</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.101100000000001</v>
+        <v>6.4618</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.953000000000001</v>
+        <v>-8.953100000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>14.054</v>
+        <v>15.4145</v>
       </c>
       <c r="G26" t="n">
         <v>12.5062</v>
@@ -2461,7 +2461,7 @@
         <v>7.213499999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>3.853599999999999</v>
+        <v>3.853599999999998</v>
       </c>
       <c r="M26" t="n">
         <v>1.4392</v>
@@ -2482,22 +2482,22 @@
         <v>20.8303</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.826199999999999</v>
+        <v>-2.4657</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.4931</v>
+        <v>-2.493</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3331</v>
+        <v>0.02740000000000004</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6031999999999997</v>
       </c>
       <c r="W26" t="n">
-        <v>6.2791</v>
+        <v>6.279100000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.8823</v>
+        <v>-6.882299999999999</v>
       </c>
     </row>
   </sheetData>
